--- a/StructureDefinition-lmdi-organization.xlsx
+++ b/StructureDefinition-lmdi-organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.7</t>
+    <t>1.0.8</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-lmdi-organization.xlsx
+++ b/StructureDefinition-lmdi-organization.xlsx
@@ -5109,7 +5109,7 @@
         <v>74</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>73</v>

--- a/StructureDefinition-lmdi-organization.xlsx
+++ b/StructureDefinition-lmdi-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2889" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2889" uniqueCount="484">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.8</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -983,7 +983,10 @@
     <t>organisatoriskBetegnelse</t>
   </si>
   <si>
-    <t>Organisatorisk betegnelse</t>
+    <t>Organisatorisk betegnelse. Kodeverk "Organisatorisk betegnelse" (OID 8624)</t>
+  </si>
+  <si>
+    <t>Kode fra kodeverk "Organisatorisk betegnelse" (OID 8624) som beskriver type organisatorisk enhet (f.eks. sykehus, avdeling, klinikk)</t>
   </si>
   <si>
     <t>urn:oid:2.16.578.1.12.4.1.1.8624</t>
@@ -6363,7 +6366,7 @@
         <v>308</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>248</v>
+        <v>309</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>239</v>
@@ -6400,7 +6403,7 @@
         <v>242</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>73</v>
@@ -6435,7 +6438,7 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>251</v>
@@ -6535,7 +6538,7 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>253</v>
@@ -6637,7 +6640,7 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>255</v>
@@ -6741,7 +6744,7 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>263</v>
@@ -6841,7 +6844,7 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>265</v>
@@ -6943,7 +6946,7 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>267</v>
@@ -6988,7 +6991,7 @@
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>73</v>
@@ -7047,7 +7050,7 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>274</v>
@@ -7149,7 +7152,7 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>280</v>
@@ -7253,7 +7256,7 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>287</v>
@@ -7357,7 +7360,7 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>293</v>
@@ -7461,7 +7464,7 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>300</v>
@@ -7565,10 +7568,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7594,16 +7597,16 @@
         <v>155</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>73</v>
@@ -7652,7 +7655,7 @@
         <v>73</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>74</v>
@@ -7669,10 +7672,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7698,16 +7701,16 @@
         <v>155</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>73</v>
@@ -7756,7 +7759,7 @@
         <v>73</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>74</v>
@@ -7773,10 +7776,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7799,19 +7802,19 @@
         <v>73</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>73</v>
@@ -7860,7 +7863,7 @@
         <v>73</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>74</v>
@@ -7869,18 +7872,18 @@
         <v>75</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7903,19 +7906,19 @@
         <v>73</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>73</v>
@@ -7964,7 +7967,7 @@
         <v>73</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>74</v>
@@ -7973,18 +7976,18 @@
         <v>75</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8081,10 +8084,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8183,13 +8186,13 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="B62" t="s" s="2">
-        <v>348</v>
-      </c>
       <c r="C62" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>73</v>
@@ -8211,13 +8214,13 @@
         <v>73</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8285,16 +8288,16 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8313,13 +8316,13 @@
         <v>73</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8387,13 +8390,13 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>73</v>
@@ -8415,13 +8418,13 @@
         <v>73</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8489,10 +8492,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8518,16 +8521,16 @@
         <v>102</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>73</v>
@@ -8540,7 +8543,7 @@
         <v>73</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>73</v>
@@ -8555,10 +8558,10 @@
         <v>169</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>73</v>
@@ -8576,7 +8579,7 @@
         <v>73</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>74</v>
@@ -8593,10 +8596,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8622,13 +8625,13 @@
         <v>102</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -8639,10 +8642,10 @@
         <v>73</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="T66" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="U66" t="s" s="2">
         <v>73</v>
@@ -8658,7 +8661,7 @@
       </c>
       <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>73</v>
@@ -8676,7 +8679,7 @@
         <v>73</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>74</v>
@@ -8693,10 +8696,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8722,16 +8725,16 @@
         <v>155</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>73</v>
@@ -8744,7 +8747,7 @@
         <v>73</v>
       </c>
       <c r="T67" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="U67" t="s" s="2">
         <v>73</v>
@@ -8780,7 +8783,7 @@
         <v>73</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>74</v>
@@ -8797,10 +8800,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8826,10 +8829,10 @@
         <v>155</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>283</v>
@@ -8846,7 +8849,7 @@
         <v>73</v>
       </c>
       <c r="T68" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="U68" t="s" s="2">
         <v>73</v>
@@ -8882,7 +8885,7 @@
         <v>73</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>74</v>
@@ -8899,14 +8902,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -8928,10 +8931,10 @@
         <v>155</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>283</v>
@@ -8948,7 +8951,7 @@
         <v>73</v>
       </c>
       <c r="T69" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="U69" t="s" s="2">
         <v>73</v>
@@ -8984,7 +8987,7 @@
         <v>73</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>74</v>
@@ -9001,14 +9004,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -9030,13 +9033,13 @@
         <v>155</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9050,7 +9053,7 @@
         <v>73</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>73</v>
@@ -9086,7 +9089,7 @@
         <v>73</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>74</v>
@@ -9103,10 +9106,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9203,10 +9206,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9305,13 +9308,13 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B73" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="B73" t="s" s="2">
-        <v>407</v>
-      </c>
       <c r="C73" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>73</v>
@@ -9333,13 +9336,13 @@
         <v>73</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9407,10 +9410,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9436,10 +9439,10 @@
         <v>155</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9463,7 +9466,7 @@
         <v>73</v>
       </c>
       <c r="W74" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="X74" t="s" s="2">
         <v>73</v>
@@ -9490,7 +9493,7 @@
         <v>73</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>74</v>
@@ -9507,14 +9510,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -9536,10 +9539,10 @@
         <v>155</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>283</v>
@@ -9592,7 +9595,7 @@
         <v>73</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>74</v>
@@ -9609,14 +9612,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -9638,10 +9641,10 @@
         <v>155</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>283</v>
@@ -9658,7 +9661,7 @@
         <v>73</v>
       </c>
       <c r="T76" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="U76" t="s" s="2">
         <v>73</v>
@@ -9694,7 +9697,7 @@
         <v>73</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>74</v>
@@ -9711,10 +9714,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9740,13 +9743,13 @@
         <v>155</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -9796,7 +9799,7 @@
         <v>73</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>74</v>
@@ -9813,10 +9816,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9842,16 +9845,16 @@
         <v>202</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>205</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>73</v>
@@ -9864,7 +9867,7 @@
         <v>73</v>
       </c>
       <c r="T78" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="U78" t="s" s="2">
         <v>73</v>
@@ -9900,7 +9903,7 @@
         <v>73</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>74</v>
@@ -9917,10 +9920,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9943,19 +9946,19 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>73</v>
@@ -10004,7 +10007,7 @@
         <v>73</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>74</v>
@@ -10021,10 +10024,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10047,19 +10050,19 @@
         <v>73</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>73</v>
@@ -10108,7 +10111,7 @@
         <v>73</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>74</v>
@@ -10125,10 +10128,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10225,10 +10228,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10327,14 +10330,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -10356,10 +10359,10 @@
         <v>126</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>129</v>
@@ -10414,7 +10417,7 @@
         <v>73</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>74</v>
@@ -10431,10 +10434,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10460,16 +10463,16 @@
         <v>175</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>73</v>
@@ -10497,10 +10500,10 @@
         <v>180</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>73</v>
@@ -10518,7 +10521,7 @@
         <v>73</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>74</v>
@@ -10535,10 +10538,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10561,19 +10564,19 @@
         <v>73</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>73</v>
@@ -10622,7 +10625,7 @@
         <v>73</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>74</v>
@@ -10639,10 +10642,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10665,17 +10668,17 @@
         <v>73</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>73</v>
@@ -10724,7 +10727,7 @@
         <v>73</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>74</v>
@@ -10736,15 +10739,15 @@
         <v>93</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10767,19 +10770,19 @@
         <v>73</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>73</v>
@@ -10828,7 +10831,7 @@
         <v>73</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>74</v>
@@ -10845,10 +10848,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10871,19 +10874,19 @@
         <v>73</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>73</v>
@@ -10932,7 +10935,7 @@
         <v>73</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>74</v>

--- a/StructureDefinition-lmdi-organization.xlsx
+++ b/StructureDefinition-lmdi-organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -84,14 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Organisasjoner i norsk helse- og omsorgstjeneste, som post, avdeling, klinikk, sykehus og sykehjem, basert på no-basis-Organization.
-Denne profilen av Organization benyttes for å beskrive helseinstitusjoner og skal representere organisasjonen på lavest mulig nivå i organisasjonshierarkiet (f.eks. en avdeling eller klinikk eller post). For organisasjonen som er del av en større organisasjon, skal dette angis ved hjelp av partOf-relasjonen.
-Det er ønskelig at minimum følgende inngår i "organisasjonshierarkiet":
-- organisasjonen på lavest mulig nivå (dvs. post, enhet, avdeling eller lignende)
-- organisasjonen på høyre nivå
-     - sykehus, Helseforetak og Regionalt Helseforetak
-     - sykehjem, kommune
-- minst ett organisasjonsnummer fra enten Enhetsregisteret (identifier:ENH) eller Register for enheter i spesialisthelsetjenesten (identifier:RSH)</t>
+    <t>Organisasjoner i norsk helse- og omsorgstjeneste, som post, avdeling, klinikk, sykehus og sykehjem. Basert på no-basis-Organization.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/StructureDefinition-lmdi-organization.xlsx
+++ b/StructureDefinition-lmdi-organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.1</t>
+    <t>1.1.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/StructureDefinition-lmdi-organization.xlsx
+++ b/StructureDefinition-lmdi-organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.1.4</t>
   </si>
   <si>
     <t>Name</t>
